--- a/scratch/Data_DPT_Pemilih_Pilketos.xlsx
+++ b/scratch/Data_DPT_Pemilih_Pilketos.xlsx
@@ -451,13 +451,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D774"/>
+  <dimension ref="A1:E774"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -481,6 +482,11 @@
           <t>Kategori (X/XI/XII/GURU/TENDIK)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Jenis Kelamin (L/P)</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -503,6 +509,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -525,6 +536,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -547,6 +563,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -569,6 +590,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -591,6 +617,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -613,6 +644,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -635,6 +671,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -657,6 +698,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -679,6 +725,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
@@ -701,6 +752,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -723,6 +779,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -745,6 +806,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -767,6 +833,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
@@ -789,6 +860,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -811,6 +887,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
@@ -833,6 +914,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -855,6 +941,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
@@ -877,6 +968,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -899,6 +995,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
@@ -921,6 +1022,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -943,6 +1049,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
@@ -965,6 +1076,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -987,6 +1103,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
@@ -1009,6 +1130,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -1031,6 +1157,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
@@ -1053,6 +1184,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
@@ -1075,6 +1211,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
@@ -1097,6 +1238,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
@@ -1119,6 +1265,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
@@ -1141,6 +1292,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -1163,6 +1319,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
@@ -1185,6 +1346,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
@@ -1207,6 +1373,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
@@ -1229,6 +1400,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
@@ -1251,6 +1427,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
@@ -1273,6 +1454,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
@@ -1295,6 +1481,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
@@ -1317,6 +1508,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
@@ -1339,6 +1535,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
@@ -1361,6 +1562,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
@@ -1383,6 +1589,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
@@ -1405,6 +1616,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
@@ -1427,6 +1643,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
@@ -1449,6 +1670,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
@@ -1471,6 +1697,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
@@ -1493,6 +1724,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
@@ -1515,6 +1751,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
@@ -1537,6 +1778,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
@@ -1559,6 +1805,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
@@ -1581,6 +1832,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
@@ -1603,6 +1859,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
@@ -1625,6 +1886,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
@@ -1647,6 +1913,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
@@ -1669,6 +1940,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
@@ -1691,6 +1967,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
@@ -1713,6 +1994,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
@@ -1735,6 +2021,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
@@ -1757,6 +2048,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
@@ -1779,6 +2075,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
@@ -1801,6 +2102,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
@@ -1823,6 +2129,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
@@ -1845,6 +2156,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
@@ -1867,6 +2183,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
@@ -1889,6 +2210,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
@@ -1911,6 +2237,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
@@ -1933,6 +2264,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
@@ -1955,6 +2291,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
@@ -1977,6 +2318,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
@@ -1999,6 +2345,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
@@ -2021,6 +2372,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
@@ -2043,6 +2399,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
@@ -2065,6 +2426,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
@@ -2087,6 +2453,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
@@ -2109,6 +2480,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
@@ -2131,6 +2507,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
@@ -2153,6 +2534,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
@@ -2175,6 +2561,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="20" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
@@ -2197,6 +2588,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="20" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
@@ -2219,6 +2615,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="20" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
@@ -2241,6 +2642,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="20" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
@@ -2263,6 +2669,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="20" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
@@ -2285,6 +2696,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="20" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
@@ -2307,6 +2723,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="20" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
@@ -2329,6 +2750,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="20" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
@@ -2351,6 +2777,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="20" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
@@ -2373,6 +2804,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="20" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
@@ -2395,6 +2831,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="20" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
@@ -2417,6 +2858,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="20" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
@@ -2439,6 +2885,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="20" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
@@ -2461,6 +2912,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="20" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
@@ -2483,6 +2939,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="20" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
@@ -2505,6 +2966,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="20" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
@@ -2527,6 +2993,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="20" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
@@ -2549,6 +3020,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="20" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
@@ -2571,6 +3047,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="20" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
@@ -2593,6 +3074,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="20" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
@@ -2615,6 +3101,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="20" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
@@ -2637,6 +3128,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="20" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
@@ -2659,6 +3155,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="20" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
@@ -2681,6 +3182,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="20" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
@@ -2703,6 +3209,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="20" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
@@ -2725,6 +3236,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="20" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
@@ -2747,6 +3263,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="20" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
@@ -2769,6 +3290,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="20" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
@@ -2791,6 +3317,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="20" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
@@ -2813,6 +3344,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="20" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
@@ -2835,6 +3371,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="20" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
@@ -2857,6 +3398,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="20" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
@@ -2879,6 +3425,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="20" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
@@ -2901,6 +3452,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="20" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
@@ -2923,6 +3479,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="20" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
@@ -2945,6 +3506,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="20" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
@@ -2967,6 +3533,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="20" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
@@ -2989,6 +3560,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="20" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
@@ -3011,6 +3587,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="20" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
@@ -3033,6 +3614,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="20" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
@@ -3055,6 +3641,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="20" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
@@ -3077,6 +3668,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="20" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
@@ -3099,6 +3695,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="20" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
@@ -3121,6 +3722,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="20" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
@@ -3143,6 +3749,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="20" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
@@ -3165,6 +3776,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="20" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
@@ -3187,6 +3803,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="20" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
@@ -3209,6 +3830,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="20" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
@@ -3231,6 +3857,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="20" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
@@ -3253,6 +3884,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="20" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
@@ -3275,6 +3911,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="20" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
@@ -3297,6 +3938,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="20" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
@@ -3319,6 +3965,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E130" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="20" customHeight="1">
       <c r="A131" s="2" t="inlineStr">
@@ -3341,6 +3992,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="20" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
@@ -3363,6 +4019,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="20" customHeight="1">
       <c r="A133" s="2" t="inlineStr">
@@ -3385,6 +4046,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="20" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
@@ -3407,6 +4073,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="20" customHeight="1">
       <c r="A135" s="2" t="inlineStr">
@@ -3429,6 +4100,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E135" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="20" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
@@ -3451,6 +4127,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E136" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="20" customHeight="1">
       <c r="A137" s="2" t="inlineStr">
@@ -3473,6 +4154,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="20" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
@@ -3495,6 +4181,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E138" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="20" customHeight="1">
       <c r="A139" s="2" t="inlineStr">
@@ -3517,6 +4208,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="20" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
@@ -3539,6 +4235,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="20" customHeight="1">
       <c r="A141" s="2" t="inlineStr">
@@ -3561,6 +4262,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="20" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
@@ -3583,6 +4289,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="20" customHeight="1">
       <c r="A143" s="2" t="inlineStr">
@@ -3605,6 +4316,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="20" customHeight="1">
       <c r="A144" s="2" t="inlineStr">
@@ -3627,6 +4343,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="20" customHeight="1">
       <c r="A145" s="2" t="inlineStr">
@@ -3649,6 +4370,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="20" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
@@ -3671,6 +4397,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E146" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="20" customHeight="1">
       <c r="A147" s="2" t="inlineStr">
@@ -3693,6 +4424,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="20" customHeight="1">
       <c r="A148" s="2" t="inlineStr">
@@ -3715,6 +4451,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E148" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="20" customHeight="1">
       <c r="A149" s="2" t="inlineStr">
@@ -3737,6 +4478,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E149" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="20" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
@@ -3759,6 +4505,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E150" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="20" customHeight="1">
       <c r="A151" s="2" t="inlineStr">
@@ -3781,6 +4532,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E151" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="20" customHeight="1">
       <c r="A152" s="2" t="inlineStr">
@@ -3803,6 +4559,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E152" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="20" customHeight="1">
       <c r="A153" s="2" t="inlineStr">
@@ -3825,6 +4586,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="20" customHeight="1">
       <c r="A154" s="2" t="inlineStr">
@@ -3847,6 +4613,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="20" customHeight="1">
       <c r="A155" s="2" t="inlineStr">
@@ -3869,6 +4640,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E155" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="20" customHeight="1">
       <c r="A156" s="2" t="inlineStr">
@@ -3891,6 +4667,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E156" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="20" customHeight="1">
       <c r="A157" s="2" t="inlineStr">
@@ -3913,6 +4694,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E157" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="20" customHeight="1">
       <c r="A158" s="2" t="inlineStr">
@@ -3935,6 +4721,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E158" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="20" customHeight="1">
       <c r="A159" s="2" t="inlineStr">
@@ -3957,6 +4748,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E159" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="20" customHeight="1">
       <c r="A160" s="2" t="inlineStr">
@@ -3979,6 +4775,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E160" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="20" customHeight="1">
       <c r="A161" s="2" t="inlineStr">
@@ -4001,6 +4802,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E161" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="20" customHeight="1">
       <c r="A162" s="2" t="inlineStr">
@@ -4023,6 +4829,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E162" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="20" customHeight="1">
       <c r="A163" s="2" t="inlineStr">
@@ -4045,6 +4856,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E163" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="20" customHeight="1">
       <c r="A164" s="2" t="inlineStr">
@@ -4067,6 +4883,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E164" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="165" ht="20" customHeight="1">
       <c r="A165" s="2" t="inlineStr">
@@ -4089,6 +4910,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E165" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="20" customHeight="1">
       <c r="A166" s="2" t="inlineStr">
@@ -4111,6 +4937,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E166" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="20" customHeight="1">
       <c r="A167" s="2" t="inlineStr">
@@ -4133,6 +4964,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E167" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="20" customHeight="1">
       <c r="A168" s="2" t="inlineStr">
@@ -4155,6 +4991,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E168" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="20" customHeight="1">
       <c r="A169" s="2" t="inlineStr">
@@ -4177,6 +5018,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E169" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="20" customHeight="1">
       <c r="A170" s="2" t="inlineStr">
@@ -4199,6 +5045,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E170" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="20" customHeight="1">
       <c r="A171" s="2" t="inlineStr">
@@ -4221,6 +5072,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E171" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="20" customHeight="1">
       <c r="A172" s="2" t="inlineStr">
@@ -4243,6 +5099,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E172" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="173" ht="20" customHeight="1">
       <c r="A173" s="2" t="inlineStr">
@@ -4265,6 +5126,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E173" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="20" customHeight="1">
       <c r="A174" s="2" t="inlineStr">
@@ -4287,6 +5153,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E174" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="175" ht="20" customHeight="1">
       <c r="A175" s="2" t="inlineStr">
@@ -4309,6 +5180,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E175" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="20" customHeight="1">
       <c r="A176" s="2" t="inlineStr">
@@ -4331,6 +5207,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E176" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="177" ht="20" customHeight="1">
       <c r="A177" s="2" t="inlineStr">
@@ -4353,6 +5234,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E177" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="178" ht="20" customHeight="1">
       <c r="A178" s="2" t="inlineStr">
@@ -4375,6 +5261,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E178" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="20" customHeight="1">
       <c r="A179" s="2" t="inlineStr">
@@ -4397,6 +5288,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E179" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="180" ht="20" customHeight="1">
       <c r="A180" s="2" t="inlineStr">
@@ -4419,6 +5315,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E180" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="181" ht="20" customHeight="1">
       <c r="A181" s="2" t="inlineStr">
@@ -4441,6 +5342,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E181" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="182" ht="20" customHeight="1">
       <c r="A182" s="2" t="inlineStr">
@@ -4463,6 +5369,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E182" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="183" ht="20" customHeight="1">
       <c r="A183" s="2" t="inlineStr">
@@ -4485,6 +5396,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E183" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="20" customHeight="1">
       <c r="A184" s="2" t="inlineStr">
@@ -4507,6 +5423,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E184" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="185" ht="20" customHeight="1">
       <c r="A185" s="2" t="inlineStr">
@@ -4529,6 +5450,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E185" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="20" customHeight="1">
       <c r="A186" s="2" t="inlineStr">
@@ -4551,6 +5477,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E186" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="187" ht="20" customHeight="1">
       <c r="A187" s="2" t="inlineStr">
@@ -4573,6 +5504,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E187" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="188" ht="20" customHeight="1">
       <c r="A188" s="2" t="inlineStr">
@@ -4595,6 +5531,11 @@
           <t>X</t>
         </is>
       </c>
+      <c r="E188" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="189" ht="20" customHeight="1">
       <c r="A189" s="2" t="inlineStr">
@@ -4617,6 +5558,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E189" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="190" ht="20" customHeight="1">
       <c r="A190" s="2" t="inlineStr">
@@ -4639,6 +5585,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E190" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="191" ht="20" customHeight="1">
       <c r="A191" s="2" t="inlineStr">
@@ -4661,6 +5612,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E191" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="192" ht="20" customHeight="1">
       <c r="A192" s="2" t="inlineStr">
@@ -4683,6 +5639,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E192" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="20" customHeight="1">
       <c r="A193" s="2" t="inlineStr">
@@ -4705,6 +5666,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E193" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="194" ht="20" customHeight="1">
       <c r="A194" s="2" t="inlineStr">
@@ -4727,6 +5693,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E194" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="195" ht="20" customHeight="1">
       <c r="A195" s="2" t="inlineStr">
@@ -4749,6 +5720,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E195" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="196" ht="20" customHeight="1">
       <c r="A196" s="2" t="inlineStr">
@@ -4771,6 +5747,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E196" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="197" ht="20" customHeight="1">
       <c r="A197" s="2" t="inlineStr">
@@ -4793,6 +5774,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E197" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="198" ht="20" customHeight="1">
       <c r="A198" s="2" t="inlineStr">
@@ -4815,6 +5801,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E198" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="199" ht="20" customHeight="1">
       <c r="A199" s="2" t="inlineStr">
@@ -4837,6 +5828,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E199" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="200" ht="20" customHeight="1">
       <c r="A200" s="2" t="inlineStr">
@@ -4859,6 +5855,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E200" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="201" ht="20" customHeight="1">
       <c r="A201" s="2" t="inlineStr">
@@ -4881,6 +5882,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E201" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="202" ht="20" customHeight="1">
       <c r="A202" s="2" t="inlineStr">
@@ -4903,6 +5909,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E202" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="203" ht="20" customHeight="1">
       <c r="A203" s="2" t="inlineStr">
@@ -4925,6 +5936,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E203" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="204" ht="20" customHeight="1">
       <c r="A204" s="2" t="inlineStr">
@@ -4947,6 +5963,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E204" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="205" ht="20" customHeight="1">
       <c r="A205" s="2" t="inlineStr">
@@ -4969,6 +5990,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E205" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="206" ht="20" customHeight="1">
       <c r="A206" s="2" t="inlineStr">
@@ -4991,6 +6017,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E206" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="207" ht="20" customHeight="1">
       <c r="A207" s="2" t="inlineStr">
@@ -5013,6 +6044,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E207" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="208" ht="20" customHeight="1">
       <c r="A208" s="2" t="inlineStr">
@@ -5035,6 +6071,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E208" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="209" ht="20" customHeight="1">
       <c r="A209" s="2" t="inlineStr">
@@ -5057,6 +6098,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E209" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="210" ht="20" customHeight="1">
       <c r="A210" s="2" t="inlineStr">
@@ -5079,6 +6125,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E210" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="211" ht="20" customHeight="1">
       <c r="A211" s="2" t="inlineStr">
@@ -5101,6 +6152,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E211" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="212" ht="20" customHeight="1">
       <c r="A212" s="2" t="inlineStr">
@@ -5123,6 +6179,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E212" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="213" ht="20" customHeight="1">
       <c r="A213" s="2" t="inlineStr">
@@ -5145,6 +6206,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E213" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="214" ht="20" customHeight="1">
       <c r="A214" s="2" t="inlineStr">
@@ -5167,6 +6233,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E214" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="215" ht="20" customHeight="1">
       <c r="A215" s="2" t="inlineStr">
@@ -5189,6 +6260,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E215" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="216" ht="20" customHeight="1">
       <c r="A216" s="2" t="inlineStr">
@@ -5211,6 +6287,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E216" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="217" ht="20" customHeight="1">
       <c r="A217" s="2" t="inlineStr">
@@ -5233,6 +6314,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E217" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="218" ht="20" customHeight="1">
       <c r="A218" s="2" t="inlineStr">
@@ -5255,6 +6341,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E218" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="219" ht="20" customHeight="1">
       <c r="A219" s="2" t="inlineStr">
@@ -5277,6 +6368,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E219" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="220" ht="20" customHeight="1">
       <c r="A220" s="2" t="inlineStr">
@@ -5299,6 +6395,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E220" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="221" ht="20" customHeight="1">
       <c r="A221" s="2" t="inlineStr">
@@ -5321,6 +6422,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E221" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="222" ht="20" customHeight="1">
       <c r="A222" s="2" t="inlineStr">
@@ -5343,6 +6449,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E222" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="223" ht="20" customHeight="1">
       <c r="A223" s="2" t="inlineStr">
@@ -5365,6 +6476,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E223" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="224" ht="20" customHeight="1">
       <c r="A224" s="2" t="inlineStr">
@@ -5387,6 +6503,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E224" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="225" ht="20" customHeight="1">
       <c r="A225" s="2" t="inlineStr">
@@ -5409,6 +6530,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E225" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="226" ht="20" customHeight="1">
       <c r="A226" s="2" t="inlineStr">
@@ -5431,6 +6557,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E226" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="227" ht="20" customHeight="1">
       <c r="A227" s="2" t="inlineStr">
@@ -5453,6 +6584,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E227" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="228" ht="20" customHeight="1">
       <c r="A228" s="2" t="inlineStr">
@@ -5475,6 +6611,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E228" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="229" ht="20" customHeight="1">
       <c r="A229" s="2" t="inlineStr">
@@ -5497,6 +6638,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E229" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="230" ht="20" customHeight="1">
       <c r="A230" s="2" t="inlineStr">
@@ -5519,6 +6665,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E230" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="231" ht="20" customHeight="1">
       <c r="A231" s="2" t="inlineStr">
@@ -5541,6 +6692,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E231" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="232" ht="20" customHeight="1">
       <c r="A232" s="2" t="inlineStr">
@@ -5563,6 +6719,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E232" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="233" ht="20" customHeight="1">
       <c r="A233" s="2" t="inlineStr">
@@ -5585,6 +6746,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E233" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="234" ht="20" customHeight="1">
       <c r="A234" s="2" t="inlineStr">
@@ -5607,6 +6773,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E234" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="235" ht="20" customHeight="1">
       <c r="A235" s="2" t="inlineStr">
@@ -5629,6 +6800,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E235" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="236" ht="20" customHeight="1">
       <c r="A236" s="2" t="inlineStr">
@@ -5651,6 +6827,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E236" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="237" ht="20" customHeight="1">
       <c r="A237" s="2" t="inlineStr">
@@ -5673,6 +6854,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E237" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="238" ht="20" customHeight="1">
       <c r="A238" s="2" t="inlineStr">
@@ -5695,6 +6881,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E238" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="239" ht="20" customHeight="1">
       <c r="A239" s="2" t="inlineStr">
@@ -5717,6 +6908,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E239" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="240" ht="20" customHeight="1">
       <c r="A240" s="2" t="inlineStr">
@@ -5739,6 +6935,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E240" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="241" ht="20" customHeight="1">
       <c r="A241" s="2" t="inlineStr">
@@ -5761,6 +6962,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E241" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="242" ht="20" customHeight="1">
       <c r="A242" s="2" t="inlineStr">
@@ -5783,6 +6989,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E242" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="243" ht="20" customHeight="1">
       <c r="A243" s="2" t="inlineStr">
@@ -5805,6 +7016,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E243" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="244" ht="20" customHeight="1">
       <c r="A244" s="2" t="inlineStr">
@@ -5827,6 +7043,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E244" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="245" ht="20" customHeight="1">
       <c r="A245" s="2" t="inlineStr">
@@ -5849,6 +7070,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E245" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="246" ht="20" customHeight="1">
       <c r="A246" s="2" t="inlineStr">
@@ -5871,6 +7097,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E246" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="247" ht="20" customHeight="1">
       <c r="A247" s="2" t="inlineStr">
@@ -5893,6 +7124,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E247" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="248" ht="20" customHeight="1">
       <c r="A248" s="2" t="inlineStr">
@@ -5915,6 +7151,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E248" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="249" ht="20" customHeight="1">
       <c r="A249" s="2" t="inlineStr">
@@ -5937,6 +7178,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E249" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="250" ht="20" customHeight="1">
       <c r="A250" s="2" t="inlineStr">
@@ -5959,6 +7205,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E250" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="251" ht="20" customHeight="1">
       <c r="A251" s="2" t="inlineStr">
@@ -5981,6 +7232,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E251" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="252" ht="20" customHeight="1">
       <c r="A252" s="2" t="inlineStr">
@@ -6003,6 +7259,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E252" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="253" ht="20" customHeight="1">
       <c r="A253" s="2" t="inlineStr">
@@ -6025,6 +7286,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E253" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="254" ht="20" customHeight="1">
       <c r="A254" s="2" t="inlineStr">
@@ -6047,6 +7313,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E254" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="255" ht="20" customHeight="1">
       <c r="A255" s="2" t="inlineStr">
@@ -6069,6 +7340,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E255" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="256" ht="20" customHeight="1">
       <c r="A256" s="2" t="inlineStr">
@@ -6091,6 +7367,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E256" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="257" ht="20" customHeight="1">
       <c r="A257" s="2" t="inlineStr">
@@ -6113,6 +7394,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E257" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="258" ht="20" customHeight="1">
       <c r="A258" s="2" t="inlineStr">
@@ -6135,6 +7421,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E258" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="259" ht="20" customHeight="1">
       <c r="A259" s="2" t="inlineStr">
@@ -6157,6 +7448,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E259" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="260" ht="20" customHeight="1">
       <c r="A260" s="2" t="inlineStr">
@@ -6179,6 +7475,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E260" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="261" ht="20" customHeight="1">
       <c r="A261" s="2" t="inlineStr">
@@ -6201,6 +7502,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E261" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="262" ht="20" customHeight="1">
       <c r="A262" s="2" t="inlineStr">
@@ -6223,6 +7529,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E262" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="263" ht="20" customHeight="1">
       <c r="A263" s="2" t="inlineStr">
@@ -6245,6 +7556,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E263" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="264" ht="20" customHeight="1">
       <c r="A264" s="2" t="inlineStr">
@@ -6267,6 +7583,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E264" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="265" ht="20" customHeight="1">
       <c r="A265" s="2" t="inlineStr">
@@ -6289,6 +7610,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E265" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="266" ht="20" customHeight="1">
       <c r="A266" s="2" t="inlineStr">
@@ -6311,6 +7637,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E266" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="267" ht="20" customHeight="1">
       <c r="A267" s="2" t="inlineStr">
@@ -6333,6 +7664,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E267" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="268" ht="20" customHeight="1">
       <c r="A268" s="2" t="inlineStr">
@@ -6355,6 +7691,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E268" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="269" ht="20" customHeight="1">
       <c r="A269" s="2" t="inlineStr">
@@ -6377,6 +7718,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E269" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="270" ht="20" customHeight="1">
       <c r="A270" s="2" t="inlineStr">
@@ -6399,6 +7745,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E270" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="271" ht="20" customHeight="1">
       <c r="A271" s="2" t="inlineStr">
@@ -6421,6 +7772,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E271" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="272" ht="20" customHeight="1">
       <c r="A272" s="2" t="inlineStr">
@@ -6443,6 +7799,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E272" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="273" ht="20" customHeight="1">
       <c r="A273" s="2" t="inlineStr">
@@ -6465,6 +7826,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E273" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="274" ht="20" customHeight="1">
       <c r="A274" s="2" t="inlineStr">
@@ -6487,6 +7853,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E274" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="275" ht="20" customHeight="1">
       <c r="A275" s="2" t="inlineStr">
@@ -6509,6 +7880,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E275" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="276" ht="20" customHeight="1">
       <c r="A276" s="2" t="inlineStr">
@@ -6531,6 +7907,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E276" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="277" ht="20" customHeight="1">
       <c r="A277" s="2" t="inlineStr">
@@ -6553,6 +7934,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E277" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="278" ht="20" customHeight="1">
       <c r="A278" s="2" t="inlineStr">
@@ -6575,6 +7961,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E278" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="279" ht="20" customHeight="1">
       <c r="A279" s="2" t="inlineStr">
@@ -6597,6 +7988,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E279" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="280" ht="20" customHeight="1">
       <c r="A280" s="2" t="inlineStr">
@@ -6619,6 +8015,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E280" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="281" ht="20" customHeight="1">
       <c r="A281" s="2" t="inlineStr">
@@ -6641,6 +8042,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E281" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="282" ht="20" customHeight="1">
       <c r="A282" s="2" t="inlineStr">
@@ -6663,6 +8069,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E282" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="283" ht="20" customHeight="1">
       <c r="A283" s="2" t="inlineStr">
@@ -6685,6 +8096,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E283" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="284" ht="20" customHeight="1">
       <c r="A284" s="2" t="inlineStr">
@@ -6707,6 +8123,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E284" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="285" ht="20" customHeight="1">
       <c r="A285" s="2" t="inlineStr">
@@ -6729,6 +8150,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E285" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="286" ht="20" customHeight="1">
       <c r="A286" s="2" t="inlineStr">
@@ -6751,6 +8177,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E286" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="287" ht="20" customHeight="1">
       <c r="A287" s="2" t="inlineStr">
@@ -6773,6 +8204,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E287" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="288" ht="20" customHeight="1">
       <c r="A288" s="2" t="inlineStr">
@@ -6795,6 +8231,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E288" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="289" ht="20" customHeight="1">
       <c r="A289" s="2" t="inlineStr">
@@ -6817,6 +8258,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E289" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="290" ht="20" customHeight="1">
       <c r="A290" s="2" t="inlineStr">
@@ -6839,6 +8285,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E290" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="291" ht="20" customHeight="1">
       <c r="A291" s="2" t="inlineStr">
@@ -6861,6 +8312,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E291" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="292" ht="20" customHeight="1">
       <c r="A292" s="2" t="inlineStr">
@@ -6883,6 +8339,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E292" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="293" ht="20" customHeight="1">
       <c r="A293" s="2" t="inlineStr">
@@ -6905,6 +8366,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E293" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="294" ht="20" customHeight="1">
       <c r="A294" s="2" t="inlineStr">
@@ -6927,6 +8393,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E294" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="295" ht="20" customHeight="1">
       <c r="A295" s="2" t="inlineStr">
@@ -6949,6 +8420,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E295" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="296" ht="20" customHeight="1">
       <c r="A296" s="2" t="inlineStr">
@@ -6971,6 +8447,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E296" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="297" ht="20" customHeight="1">
       <c r="A297" s="2" t="inlineStr">
@@ -6993,6 +8474,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E297" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="298" ht="20" customHeight="1">
       <c r="A298" s="2" t="inlineStr">
@@ -7015,6 +8501,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E298" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="299" ht="20" customHeight="1">
       <c r="A299" s="2" t="inlineStr">
@@ -7037,6 +8528,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E299" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="300" ht="20" customHeight="1">
       <c r="A300" s="2" t="inlineStr">
@@ -7059,6 +8555,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E300" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="301" ht="20" customHeight="1">
       <c r="A301" s="2" t="inlineStr">
@@ -7081,6 +8582,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E301" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="302" ht="20" customHeight="1">
       <c r="A302" s="2" t="inlineStr">
@@ -7103,6 +8609,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E302" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="303" ht="20" customHeight="1">
       <c r="A303" s="2" t="inlineStr">
@@ -7125,6 +8636,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E303" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="304" ht="20" customHeight="1">
       <c r="A304" s="2" t="inlineStr">
@@ -7147,6 +8663,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E304" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="305" ht="20" customHeight="1">
       <c r="A305" s="2" t="inlineStr">
@@ -7169,6 +8690,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E305" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="306" ht="20" customHeight="1">
       <c r="A306" s="2" t="inlineStr">
@@ -7191,6 +8717,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E306" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="307" ht="20" customHeight="1">
       <c r="A307" s="2" t="inlineStr">
@@ -7213,6 +8744,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E307" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="308" ht="20" customHeight="1">
       <c r="A308" s="2" t="inlineStr">
@@ -7235,6 +8771,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E308" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="309" ht="20" customHeight="1">
       <c r="A309" s="2" t="inlineStr">
@@ -7257,6 +8798,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E309" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="310" ht="20" customHeight="1">
       <c r="A310" s="2" t="inlineStr">
@@ -7279,6 +8825,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E310" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="311" ht="20" customHeight="1">
       <c r="A311" s="2" t="inlineStr">
@@ -7301,6 +8852,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E311" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="312" ht="20" customHeight="1">
       <c r="A312" s="2" t="inlineStr">
@@ -7323,6 +8879,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E312" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="313" ht="20" customHeight="1">
       <c r="A313" s="2" t="inlineStr">
@@ -7345,6 +8906,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E313" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="314" ht="20" customHeight="1">
       <c r="A314" s="2" t="inlineStr">
@@ -7367,6 +8933,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E314" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="315" ht="20" customHeight="1">
       <c r="A315" s="2" t="inlineStr">
@@ -7389,6 +8960,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E315" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="316" ht="20" customHeight="1">
       <c r="A316" s="2" t="inlineStr">
@@ -7411,6 +8987,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E316" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="317" ht="20" customHeight="1">
       <c r="A317" s="2" t="inlineStr">
@@ -7433,6 +9014,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E317" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="318" ht="20" customHeight="1">
       <c r="A318" s="2" t="inlineStr">
@@ -7455,6 +9041,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E318" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="319" ht="20" customHeight="1">
       <c r="A319" s="2" t="inlineStr">
@@ -7477,6 +9068,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E319" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="320" ht="20" customHeight="1">
       <c r="A320" s="2" t="inlineStr">
@@ -7499,6 +9095,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E320" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="321" ht="20" customHeight="1">
       <c r="A321" s="2" t="inlineStr">
@@ -7521,6 +9122,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E321" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="322" ht="20" customHeight="1">
       <c r="A322" s="2" t="inlineStr">
@@ -7543,6 +9149,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E322" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="323" ht="20" customHeight="1">
       <c r="A323" s="2" t="inlineStr">
@@ -7565,6 +9176,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E323" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="324" ht="20" customHeight="1">
       <c r="A324" s="2" t="inlineStr">
@@ -7587,6 +9203,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E324" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="325" ht="20" customHeight="1">
       <c r="A325" s="2" t="inlineStr">
@@ -7609,6 +9230,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E325" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="326" ht="20" customHeight="1">
       <c r="A326" s="2" t="inlineStr">
@@ -7631,6 +9257,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E326" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="327" ht="20" customHeight="1">
       <c r="A327" s="2" t="inlineStr">
@@ -7653,6 +9284,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E327" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="328" ht="20" customHeight="1">
       <c r="A328" s="2" t="inlineStr">
@@ -7675,6 +9311,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E328" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="329" ht="20" customHeight="1">
       <c r="A329" s="2" t="inlineStr">
@@ -7697,6 +9338,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E329" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="330" ht="20" customHeight="1">
       <c r="A330" s="2" t="inlineStr">
@@ -7719,6 +9365,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E330" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="331" ht="20" customHeight="1">
       <c r="A331" s="2" t="inlineStr">
@@ -7741,6 +9392,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E331" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="332" ht="20" customHeight="1">
       <c r="A332" s="2" t="inlineStr">
@@ -7763,6 +9419,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E332" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="333" ht="20" customHeight="1">
       <c r="A333" s="2" t="inlineStr">
@@ -7785,6 +9446,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E333" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="334" ht="20" customHeight="1">
       <c r="A334" s="2" t="inlineStr">
@@ -7807,6 +9473,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E334" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="335" ht="20" customHeight="1">
       <c r="A335" s="2" t="inlineStr">
@@ -7829,6 +9500,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E335" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="336" ht="20" customHeight="1">
       <c r="A336" s="2" t="inlineStr">
@@ -7851,6 +9527,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E336" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="337" ht="20" customHeight="1">
       <c r="A337" s="2" t="inlineStr">
@@ -7873,6 +9554,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E337" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="338" ht="20" customHeight="1">
       <c r="A338" s="2" t="inlineStr">
@@ -7895,6 +9581,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E338" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="339" ht="20" customHeight="1">
       <c r="A339" s="2" t="inlineStr">
@@ -7917,6 +9608,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E339" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="340" ht="20" customHeight="1">
       <c r="A340" s="2" t="inlineStr">
@@ -7939,6 +9635,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E340" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="341" ht="20" customHeight="1">
       <c r="A341" s="2" t="inlineStr">
@@ -7961,6 +9662,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E341" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="342" ht="20" customHeight="1">
       <c r="A342" s="2" t="inlineStr">
@@ -7983,6 +9689,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E342" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="343" ht="20" customHeight="1">
       <c r="A343" s="2" t="inlineStr">
@@ -8005,6 +9716,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E343" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="344" ht="20" customHeight="1">
       <c r="A344" s="2" t="inlineStr">
@@ -8027,6 +9743,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E344" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="345" ht="20" customHeight="1">
       <c r="A345" s="2" t="inlineStr">
@@ -8049,6 +9770,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E345" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="346" ht="20" customHeight="1">
       <c r="A346" s="2" t="inlineStr">
@@ -8071,6 +9797,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E346" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="347" ht="20" customHeight="1">
       <c r="A347" s="2" t="inlineStr">
@@ -8093,6 +9824,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E347" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="348" ht="20" customHeight="1">
       <c r="A348" s="2" t="inlineStr">
@@ -8115,6 +9851,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E348" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="349" ht="20" customHeight="1">
       <c r="A349" s="2" t="inlineStr">
@@ -8137,6 +9878,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E349" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="350" ht="20" customHeight="1">
       <c r="A350" s="2" t="inlineStr">
@@ -8159,6 +9905,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E350" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="351" ht="20" customHeight="1">
       <c r="A351" s="2" t="inlineStr">
@@ -8181,6 +9932,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E351" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="352" ht="20" customHeight="1">
       <c r="A352" s="2" t="inlineStr">
@@ -8203,6 +9959,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E352" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="353" ht="20" customHeight="1">
       <c r="A353" s="2" t="inlineStr">
@@ -8225,6 +9986,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E353" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="354" ht="20" customHeight="1">
       <c r="A354" s="2" t="inlineStr">
@@ -8247,6 +10013,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E354" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="355" ht="20" customHeight="1">
       <c r="A355" s="2" t="inlineStr">
@@ -8269,6 +10040,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E355" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="356" ht="20" customHeight="1">
       <c r="A356" s="2" t="inlineStr">
@@ -8291,6 +10067,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E356" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="357" ht="20" customHeight="1">
       <c r="A357" s="2" t="inlineStr">
@@ -8313,6 +10094,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E357" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="358" ht="20" customHeight="1">
       <c r="A358" s="2" t="inlineStr">
@@ -8335,6 +10121,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E358" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="359" ht="20" customHeight="1">
       <c r="A359" s="2" t="inlineStr">
@@ -8357,6 +10148,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E359" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="360" ht="20" customHeight="1">
       <c r="A360" s="2" t="inlineStr">
@@ -8379,6 +10175,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E360" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="361" ht="20" customHeight="1">
       <c r="A361" s="2" t="inlineStr">
@@ -8401,6 +10202,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E361" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="362" ht="20" customHeight="1">
       <c r="A362" s="2" t="inlineStr">
@@ -8423,6 +10229,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E362" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="363" ht="20" customHeight="1">
       <c r="A363" s="2" t="inlineStr">
@@ -8445,6 +10256,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E363" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="364" ht="20" customHeight="1">
       <c r="A364" s="2" t="inlineStr">
@@ -8467,6 +10283,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E364" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="365" ht="20" customHeight="1">
       <c r="A365" s="2" t="inlineStr">
@@ -8489,6 +10310,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E365" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="366" ht="20" customHeight="1">
       <c r="A366" s="2" t="inlineStr">
@@ -8511,6 +10337,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E366" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="367" ht="20" customHeight="1">
       <c r="A367" s="2" t="inlineStr">
@@ -8533,6 +10364,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E367" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="368" ht="20" customHeight="1">
       <c r="A368" s="2" t="inlineStr">
@@ -8555,6 +10391,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E368" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="369" ht="20" customHeight="1">
       <c r="A369" s="2" t="inlineStr">
@@ -8577,6 +10418,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E369" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="370" ht="20" customHeight="1">
       <c r="A370" s="2" t="inlineStr">
@@ -8599,6 +10445,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E370" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="371" ht="20" customHeight="1">
       <c r="A371" s="2" t="inlineStr">
@@ -8621,6 +10472,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E371" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="372" ht="20" customHeight="1">
       <c r="A372" s="2" t="inlineStr">
@@ -8643,6 +10499,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E372" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="373" ht="20" customHeight="1">
       <c r="A373" s="2" t="inlineStr">
@@ -8665,6 +10526,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E373" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="374" ht="20" customHeight="1">
       <c r="A374" s="2" t="inlineStr">
@@ -8687,6 +10553,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E374" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="375" ht="20" customHeight="1">
       <c r="A375" s="2" t="inlineStr">
@@ -8709,6 +10580,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E375" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="376" ht="20" customHeight="1">
       <c r="A376" s="2" t="inlineStr">
@@ -8731,6 +10607,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E376" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="377" ht="20" customHeight="1">
       <c r="A377" s="2" t="inlineStr">
@@ -8753,6 +10634,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E377" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="378" ht="20" customHeight="1">
       <c r="A378" s="2" t="inlineStr">
@@ -8775,6 +10661,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E378" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="379" ht="20" customHeight="1">
       <c r="A379" s="2" t="inlineStr">
@@ -8797,6 +10688,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E379" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="380" ht="20" customHeight="1">
       <c r="A380" s="2" t="inlineStr">
@@ -8819,6 +10715,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E380" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="381" ht="20" customHeight="1">
       <c r="A381" s="2" t="inlineStr">
@@ -8841,6 +10742,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E381" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="382" ht="20" customHeight="1">
       <c r="A382" s="2" t="inlineStr">
@@ -8863,6 +10769,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E382" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="383" ht="20" customHeight="1">
       <c r="A383" s="2" t="inlineStr">
@@ -8885,6 +10796,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E383" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="384" ht="20" customHeight="1">
       <c r="A384" s="2" t="inlineStr">
@@ -8907,6 +10823,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E384" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="385" ht="20" customHeight="1">
       <c r="A385" s="2" t="inlineStr">
@@ -8929,6 +10850,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E385" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="386" ht="20" customHeight="1">
       <c r="A386" s="2" t="inlineStr">
@@ -8951,6 +10877,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E386" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="387" ht="20" customHeight="1">
       <c r="A387" s="2" t="inlineStr">
@@ -8973,6 +10904,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E387" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="388" ht="20" customHeight="1">
       <c r="A388" s="2" t="inlineStr">
@@ -8995,6 +10931,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E388" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="389" ht="20" customHeight="1">
       <c r="A389" s="2" t="inlineStr">
@@ -9017,6 +10958,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E389" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="390" ht="20" customHeight="1">
       <c r="A390" s="2" t="inlineStr">
@@ -9039,6 +10985,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E390" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="391" ht="20" customHeight="1">
       <c r="A391" s="2" t="inlineStr">
@@ -9061,6 +11012,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E391" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="392" ht="20" customHeight="1">
       <c r="A392" s="2" t="inlineStr">
@@ -9083,6 +11039,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E392" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="393" ht="20" customHeight="1">
       <c r="A393" s="2" t="inlineStr">
@@ -9105,6 +11066,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E393" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="394" ht="20" customHeight="1">
       <c r="A394" s="2" t="inlineStr">
@@ -9127,6 +11093,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E394" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="395" ht="20" customHeight="1">
       <c r="A395" s="2" t="inlineStr">
@@ -9149,6 +11120,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E395" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="396" ht="20" customHeight="1">
       <c r="A396" s="2" t="inlineStr">
@@ -9171,6 +11147,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E396" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="397" ht="20" customHeight="1">
       <c r="A397" s="2" t="inlineStr">
@@ -9193,6 +11174,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E397" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="398" ht="20" customHeight="1">
       <c r="A398" s="2" t="inlineStr">
@@ -9215,6 +11201,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E398" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="399" ht="20" customHeight="1">
       <c r="A399" s="2" t="inlineStr">
@@ -9237,6 +11228,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E399" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="400" ht="20" customHeight="1">
       <c r="A400" s="2" t="inlineStr">
@@ -9259,6 +11255,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E400" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="401" ht="20" customHeight="1">
       <c r="A401" s="2" t="inlineStr">
@@ -9281,6 +11282,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E401" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="402" ht="20" customHeight="1">
       <c r="A402" s="2" t="inlineStr">
@@ -9303,6 +11309,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E402" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="403" ht="20" customHeight="1">
       <c r="A403" s="2" t="inlineStr">
@@ -9325,6 +11336,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E403" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="404" ht="20" customHeight="1">
       <c r="A404" s="2" t="inlineStr">
@@ -9347,6 +11363,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E404" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="405" ht="20" customHeight="1">
       <c r="A405" s="2" t="inlineStr">
@@ -9369,6 +11390,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E405" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="406" ht="20" customHeight="1">
       <c r="A406" s="2" t="inlineStr">
@@ -9391,6 +11417,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E406" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="407" ht="20" customHeight="1">
       <c r="A407" s="2" t="inlineStr">
@@ -9413,6 +11444,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E407" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="408" ht="20" customHeight="1">
       <c r="A408" s="2" t="inlineStr">
@@ -9435,6 +11471,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E408" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="409" ht="20" customHeight="1">
       <c r="A409" s="2" t="inlineStr">
@@ -9457,6 +11498,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E409" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="410" ht="20" customHeight="1">
       <c r="A410" s="2" t="inlineStr">
@@ -9479,6 +11525,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E410" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="411" ht="20" customHeight="1">
       <c r="A411" s="2" t="inlineStr">
@@ -9501,6 +11552,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E411" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="412" ht="20" customHeight="1">
       <c r="A412" s="2" t="inlineStr">
@@ -9523,6 +11579,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E412" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="413" ht="20" customHeight="1">
       <c r="A413" s="2" t="inlineStr">
@@ -9545,6 +11606,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E413" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="414" ht="20" customHeight="1">
       <c r="A414" s="2" t="inlineStr">
@@ -9567,6 +11633,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E414" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="415" ht="20" customHeight="1">
       <c r="A415" s="2" t="inlineStr">
@@ -9589,6 +11660,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E415" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="416" ht="20" customHeight="1">
       <c r="A416" s="2" t="inlineStr">
@@ -9611,6 +11687,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E416" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="417" ht="20" customHeight="1">
       <c r="A417" s="2" t="inlineStr">
@@ -9633,6 +11714,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E417" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="418" ht="20" customHeight="1">
       <c r="A418" s="2" t="inlineStr">
@@ -9655,6 +11741,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E418" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="419" ht="20" customHeight="1">
       <c r="A419" s="2" t="inlineStr">
@@ -9677,6 +11768,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E419" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="420" ht="20" customHeight="1">
       <c r="A420" s="2" t="inlineStr">
@@ -9699,6 +11795,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E420" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="421" ht="20" customHeight="1">
       <c r="A421" s="2" t="inlineStr">
@@ -9721,6 +11822,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E421" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="422" ht="20" customHeight="1">
       <c r="A422" s="2" t="inlineStr">
@@ -9743,6 +11849,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E422" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="423" ht="20" customHeight="1">
       <c r="A423" s="2" t="inlineStr">
@@ -9765,6 +11876,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E423" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="424" ht="20" customHeight="1">
       <c r="A424" s="2" t="inlineStr">
@@ -9787,6 +11903,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E424" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="425" ht="20" customHeight="1">
       <c r="A425" s="2" t="inlineStr">
@@ -9809,6 +11930,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E425" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="426" ht="20" customHeight="1">
       <c r="A426" s="2" t="inlineStr">
@@ -9831,6 +11957,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E426" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="427" ht="20" customHeight="1">
       <c r="A427" s="2" t="inlineStr">
@@ -9853,6 +11984,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E427" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="428" ht="20" customHeight="1">
       <c r="A428" s="2" t="inlineStr">
@@ -9875,6 +12011,11 @@
           <t>XI</t>
         </is>
       </c>
+      <c r="E428" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="429" ht="20" customHeight="1">
       <c r="A429" s="2" t="inlineStr">
@@ -9897,6 +12038,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E429" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="430" ht="20" customHeight="1">
       <c r="A430" s="2" t="inlineStr">
@@ -9919,6 +12065,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E430" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="431" ht="20" customHeight="1">
       <c r="A431" s="2" t="inlineStr">
@@ -9941,6 +12092,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E431" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="432" ht="20" customHeight="1">
       <c r="A432" s="2" t="inlineStr">
@@ -9963,6 +12119,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E432" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="433" ht="20" customHeight="1">
       <c r="A433" s="2" t="inlineStr">
@@ -9985,6 +12146,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E433" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="434" ht="20" customHeight="1">
       <c r="A434" s="2" t="inlineStr">
@@ -10007,6 +12173,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E434" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="435" ht="20" customHeight="1">
       <c r="A435" s="2" t="inlineStr">
@@ -10029,6 +12200,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E435" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="436" ht="20" customHeight="1">
       <c r="A436" s="2" t="inlineStr">
@@ -10051,6 +12227,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E436" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="437" ht="20" customHeight="1">
       <c r="A437" s="2" t="inlineStr">
@@ -10073,6 +12254,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E437" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="438" ht="20" customHeight="1">
       <c r="A438" s="2" t="inlineStr">
@@ -10095,6 +12281,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E438" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="439" ht="20" customHeight="1">
       <c r="A439" s="2" t="inlineStr">
@@ -10117,6 +12308,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E439" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="440" ht="20" customHeight="1">
       <c r="A440" s="2" t="inlineStr">
@@ -10139,6 +12335,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E440" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="441" ht="20" customHeight="1">
       <c r="A441" s="2" t="inlineStr">
@@ -10161,6 +12362,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E441" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="442" ht="20" customHeight="1">
       <c r="A442" s="2" t="inlineStr">
@@ -10183,6 +12389,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E442" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="443" ht="20" customHeight="1">
       <c r="A443" s="2" t="inlineStr">
@@ -10205,6 +12416,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E443" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="444" ht="20" customHeight="1">
       <c r="A444" s="2" t="inlineStr">
@@ -10227,6 +12443,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E444" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="445" ht="20" customHeight="1">
       <c r="A445" s="2" t="inlineStr">
@@ -10249,6 +12470,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E445" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="446" ht="20" customHeight="1">
       <c r="A446" s="2" t="inlineStr">
@@ -10271,6 +12497,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E446" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="447" ht="20" customHeight="1">
       <c r="A447" s="2" t="inlineStr">
@@ -10293,6 +12524,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E447" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="448" ht="20" customHeight="1">
       <c r="A448" s="2" t="inlineStr">
@@ -10315,6 +12551,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E448" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="449" ht="20" customHeight="1">
       <c r="A449" s="2" t="inlineStr">
@@ -10337,6 +12578,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E449" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="450" ht="20" customHeight="1">
       <c r="A450" s="2" t="inlineStr">
@@ -10359,6 +12605,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E450" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="451" ht="20" customHeight="1">
       <c r="A451" s="2" t="inlineStr">
@@ -10381,6 +12632,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E451" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="452" ht="20" customHeight="1">
       <c r="A452" s="2" t="inlineStr">
@@ -10403,6 +12659,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E452" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="453" ht="20" customHeight="1">
       <c r="A453" s="2" t="inlineStr">
@@ -10425,6 +12686,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E453" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="454" ht="20" customHeight="1">
       <c r="A454" s="2" t="inlineStr">
@@ -10447,6 +12713,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E454" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="455" ht="20" customHeight="1">
       <c r="A455" s="2" t="inlineStr">
@@ -10469,6 +12740,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E455" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="456" ht="20" customHeight="1">
       <c r="A456" s="2" t="inlineStr">
@@ -10491,6 +12767,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E456" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="457" ht="20" customHeight="1">
       <c r="A457" s="2" t="inlineStr">
@@ -10513,6 +12794,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E457" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="458" ht="20" customHeight="1">
       <c r="A458" s="2" t="inlineStr">
@@ -10535,6 +12821,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E458" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="459" ht="20" customHeight="1">
       <c r="A459" s="2" t="inlineStr">
@@ -10557,6 +12848,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E459" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="460" ht="20" customHeight="1">
       <c r="A460" s="2" t="inlineStr">
@@ -10579,6 +12875,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E460" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="461" ht="20" customHeight="1">
       <c r="A461" s="2" t="inlineStr">
@@ -10601,6 +12902,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E461" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="462" ht="20" customHeight="1">
       <c r="A462" s="2" t="inlineStr">
@@ -10623,6 +12929,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E462" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="463" ht="20" customHeight="1">
       <c r="A463" s="2" t="inlineStr">
@@ -10645,6 +12956,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E463" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="464" ht="20" customHeight="1">
       <c r="A464" s="2" t="inlineStr">
@@ -10667,6 +12983,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E464" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="465" ht="20" customHeight="1">
       <c r="A465" s="2" t="inlineStr">
@@ -10689,6 +13010,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E465" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="466" ht="20" customHeight="1">
       <c r="A466" s="2" t="inlineStr">
@@ -10711,6 +13037,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E466" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="467" ht="20" customHeight="1">
       <c r="A467" s="2" t="inlineStr">
@@ -10733,6 +13064,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E467" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="468" ht="20" customHeight="1">
       <c r="A468" s="2" t="inlineStr">
@@ -10755,6 +13091,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E468" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="469" ht="20" customHeight="1">
       <c r="A469" s="2" t="inlineStr">
@@ -10777,6 +13118,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E469" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="470" ht="20" customHeight="1">
       <c r="A470" s="2" t="inlineStr">
@@ -10799,6 +13145,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E470" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="471" ht="20" customHeight="1">
       <c r="A471" s="2" t="inlineStr">
@@ -10821,6 +13172,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E471" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="472" ht="20" customHeight="1">
       <c r="A472" s="2" t="inlineStr">
@@ -10843,6 +13199,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E472" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="473" ht="20" customHeight="1">
       <c r="A473" s="2" t="inlineStr">
@@ -10865,6 +13226,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E473" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="474" ht="20" customHeight="1">
       <c r="A474" s="2" t="inlineStr">
@@ -10887,6 +13253,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E474" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="475" ht="20" customHeight="1">
       <c r="A475" s="2" t="inlineStr">
@@ -10909,6 +13280,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E475" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="476" ht="20" customHeight="1">
       <c r="A476" s="2" t="inlineStr">
@@ -10931,6 +13307,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E476" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="477" ht="20" customHeight="1">
       <c r="A477" s="2" t="inlineStr">
@@ -10953,6 +13334,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E477" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="478" ht="20" customHeight="1">
       <c r="A478" s="2" t="inlineStr">
@@ -10975,6 +13361,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E478" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="479" ht="20" customHeight="1">
       <c r="A479" s="2" t="inlineStr">
@@ -10997,6 +13388,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E479" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="480" ht="20" customHeight="1">
       <c r="A480" s="2" t="inlineStr">
@@ -11019,6 +13415,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E480" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="481" ht="20" customHeight="1">
       <c r="A481" s="2" t="inlineStr">
@@ -11041,6 +13442,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E481" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="482" ht="20" customHeight="1">
       <c r="A482" s="2" t="inlineStr">
@@ -11063,6 +13469,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E482" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="483" ht="20" customHeight="1">
       <c r="A483" s="2" t="inlineStr">
@@ -11085,6 +13496,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E483" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="484" ht="20" customHeight="1">
       <c r="A484" s="2" t="inlineStr">
@@ -11107,6 +13523,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E484" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="485" ht="20" customHeight="1">
       <c r="A485" s="2" t="inlineStr">
@@ -11129,6 +13550,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E485" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="486" ht="20" customHeight="1">
       <c r="A486" s="2" t="inlineStr">
@@ -11151,6 +13577,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E486" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="487" ht="20" customHeight="1">
       <c r="A487" s="2" t="inlineStr">
@@ -11173,6 +13604,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E487" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="488" ht="20" customHeight="1">
       <c r="A488" s="2" t="inlineStr">
@@ -11195,6 +13631,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E488" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="489" ht="20" customHeight="1">
       <c r="A489" s="2" t="inlineStr">
@@ -11217,6 +13658,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E489" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="490" ht="20" customHeight="1">
       <c r="A490" s="2" t="inlineStr">
@@ -11239,6 +13685,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E490" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="491" ht="20" customHeight="1">
       <c r="A491" s="2" t="inlineStr">
@@ -11261,6 +13712,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E491" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="492" ht="20" customHeight="1">
       <c r="A492" s="2" t="inlineStr">
@@ -11283,6 +13739,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E492" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="493" ht="20" customHeight="1">
       <c r="A493" s="2" t="inlineStr">
@@ -11305,6 +13766,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E493" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="494" ht="20" customHeight="1">
       <c r="A494" s="2" t="inlineStr">
@@ -11327,6 +13793,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E494" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="495" ht="20" customHeight="1">
       <c r="A495" s="2" t="inlineStr">
@@ -11349,6 +13820,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E495" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="496" ht="20" customHeight="1">
       <c r="A496" s="2" t="inlineStr">
@@ -11371,6 +13847,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E496" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="497" ht="20" customHeight="1">
       <c r="A497" s="2" t="inlineStr">
@@ -11393,6 +13874,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E497" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="498" ht="20" customHeight="1">
       <c r="A498" s="2" t="inlineStr">
@@ -11415,6 +13901,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E498" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="499" ht="20" customHeight="1">
       <c r="A499" s="2" t="inlineStr">
@@ -11437,6 +13928,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E499" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="500" ht="20" customHeight="1">
       <c r="A500" s="2" t="inlineStr">
@@ -11459,6 +13955,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E500" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="501" ht="20" customHeight="1">
       <c r="A501" s="2" t="inlineStr">
@@ -11481,6 +13982,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E501" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="502" ht="20" customHeight="1">
       <c r="A502" s="2" t="inlineStr">
@@ -11503,6 +14009,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E502" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="503" ht="20" customHeight="1">
       <c r="A503" s="2" t="inlineStr">
@@ -11525,6 +14036,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E503" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="504" ht="20" customHeight="1">
       <c r="A504" s="2" t="inlineStr">
@@ -11547,6 +14063,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E504" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="505" ht="20" customHeight="1">
       <c r="A505" s="2" t="inlineStr">
@@ -11569,6 +14090,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E505" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="506" ht="20" customHeight="1">
       <c r="A506" s="2" t="inlineStr">
@@ -11591,6 +14117,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E506" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="507" ht="20" customHeight="1">
       <c r="A507" s="2" t="inlineStr">
@@ -11613,6 +14144,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E507" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="508" ht="20" customHeight="1">
       <c r="A508" s="2" t="inlineStr">
@@ -11635,6 +14171,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E508" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="509" ht="20" customHeight="1">
       <c r="A509" s="2" t="inlineStr">
@@ -11657,6 +14198,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E509" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="510" ht="20" customHeight="1">
       <c r="A510" s="2" t="inlineStr">
@@ -11679,6 +14225,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E510" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="511" ht="20" customHeight="1">
       <c r="A511" s="2" t="inlineStr">
@@ -11701,6 +14252,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E511" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="512" ht="20" customHeight="1">
       <c r="A512" s="2" t="inlineStr">
@@ -11723,6 +14279,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E512" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="513" ht="20" customHeight="1">
       <c r="A513" s="2" t="inlineStr">
@@ -11745,6 +14306,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E513" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="514" ht="20" customHeight="1">
       <c r="A514" s="2" t="inlineStr">
@@ -11767,6 +14333,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E514" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="515" ht="20" customHeight="1">
       <c r="A515" s="2" t="inlineStr">
@@ -11789,6 +14360,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E515" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="516" ht="20" customHeight="1">
       <c r="A516" s="2" t="inlineStr">
@@ -11811,6 +14387,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E516" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="517" ht="20" customHeight="1">
       <c r="A517" s="2" t="inlineStr">
@@ -11833,6 +14414,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E517" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="518" ht="20" customHeight="1">
       <c r="A518" s="2" t="inlineStr">
@@ -11855,6 +14441,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E518" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="519" ht="20" customHeight="1">
       <c r="A519" s="2" t="inlineStr">
@@ -11877,6 +14468,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E519" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="520" ht="20" customHeight="1">
       <c r="A520" s="2" t="inlineStr">
@@ -11899,6 +14495,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E520" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="521" ht="20" customHeight="1">
       <c r="A521" s="2" t="inlineStr">
@@ -11921,6 +14522,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E521" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="522" ht="20" customHeight="1">
       <c r="A522" s="2" t="inlineStr">
@@ -11943,6 +14549,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E522" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="523" ht="20" customHeight="1">
       <c r="A523" s="2" t="inlineStr">
@@ -11965,6 +14576,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E523" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="524" ht="20" customHeight="1">
       <c r="A524" s="2" t="inlineStr">
@@ -11987,6 +14603,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E524" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="525" ht="20" customHeight="1">
       <c r="A525" s="2" t="inlineStr">
@@ -12009,6 +14630,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E525" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="526" ht="20" customHeight="1">
       <c r="A526" s="2" t="inlineStr">
@@ -12031,6 +14657,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E526" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="527" ht="20" customHeight="1">
       <c r="A527" s="2" t="inlineStr">
@@ -12053,6 +14684,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E527" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="528" ht="20" customHeight="1">
       <c r="A528" s="2" t="inlineStr">
@@ -12075,6 +14711,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E528" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="529" ht="20" customHeight="1">
       <c r="A529" s="2" t="inlineStr">
@@ -12097,6 +14738,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E529" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="530" ht="20" customHeight="1">
       <c r="A530" s="2" t="inlineStr">
@@ -12119,6 +14765,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E530" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="531" ht="20" customHeight="1">
       <c r="A531" s="2" t="inlineStr">
@@ -12141,6 +14792,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E531" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="532" ht="20" customHeight="1">
       <c r="A532" s="2" t="inlineStr">
@@ -12163,6 +14819,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E532" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="533" ht="20" customHeight="1">
       <c r="A533" s="2" t="inlineStr">
@@ -12185,6 +14846,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E533" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="534" ht="20" customHeight="1">
       <c r="A534" s="2" t="inlineStr">
@@ -12207,6 +14873,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E534" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="535" ht="20" customHeight="1">
       <c r="A535" s="2" t="inlineStr">
@@ -12229,6 +14900,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E535" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="536" ht="20" customHeight="1">
       <c r="A536" s="2" t="inlineStr">
@@ -12251,6 +14927,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E536" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="537" ht="20" customHeight="1">
       <c r="A537" s="2" t="inlineStr">
@@ -12273,6 +14954,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E537" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="538" ht="20" customHeight="1">
       <c r="A538" s="2" t="inlineStr">
@@ -12295,6 +14981,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E538" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="539" ht="20" customHeight="1">
       <c r="A539" s="2" t="inlineStr">
@@ -12317,6 +15008,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E539" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="540" ht="20" customHeight="1">
       <c r="A540" s="2" t="inlineStr">
@@ -12339,6 +15035,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E540" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="541" ht="20" customHeight="1">
       <c r="A541" s="2" t="inlineStr">
@@ -12361,6 +15062,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E541" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="542" ht="20" customHeight="1">
       <c r="A542" s="2" t="inlineStr">
@@ -12383,6 +15089,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E542" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="543" ht="20" customHeight="1">
       <c r="A543" s="2" t="inlineStr">
@@ -12405,6 +15116,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E543" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="544" ht="20" customHeight="1">
       <c r="A544" s="2" t="inlineStr">
@@ -12427,6 +15143,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E544" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="545" ht="20" customHeight="1">
       <c r="A545" s="2" t="inlineStr">
@@ -12449,6 +15170,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E545" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="546" ht="20" customHeight="1">
       <c r="A546" s="2" t="inlineStr">
@@ -12471,6 +15197,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E546" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="547" ht="20" customHeight="1">
       <c r="A547" s="2" t="inlineStr">
@@ -12493,6 +15224,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E547" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="548" ht="20" customHeight="1">
       <c r="A548" s="2" t="inlineStr">
@@ -12515,6 +15251,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E548" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="549" ht="20" customHeight="1">
       <c r="A549" s="2" t="inlineStr">
@@ -12537,6 +15278,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E549" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="550" ht="20" customHeight="1">
       <c r="A550" s="2" t="inlineStr">
@@ -12559,6 +15305,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E550" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="551" ht="20" customHeight="1">
       <c r="A551" s="2" t="inlineStr">
@@ -12581,6 +15332,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E551" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="552" ht="20" customHeight="1">
       <c r="A552" s="2" t="inlineStr">
@@ -12603,6 +15359,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E552" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="553" ht="20" customHeight="1">
       <c r="A553" s="2" t="inlineStr">
@@ -12625,6 +15386,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E553" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="554" ht="20" customHeight="1">
       <c r="A554" s="2" t="inlineStr">
@@ -12647,6 +15413,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E554" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="555" ht="20" customHeight="1">
       <c r="A555" s="2" t="inlineStr">
@@ -12669,6 +15440,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E555" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="556" ht="20" customHeight="1">
       <c r="A556" s="2" t="inlineStr">
@@ -12691,6 +15467,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E556" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="557" ht="20" customHeight="1">
       <c r="A557" s="2" t="inlineStr">
@@ -12713,6 +15494,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E557" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="558" ht="20" customHeight="1">
       <c r="A558" s="2" t="inlineStr">
@@ -12735,6 +15521,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E558" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="559" ht="20" customHeight="1">
       <c r="A559" s="2" t="inlineStr">
@@ -12757,6 +15548,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E559" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="560" ht="20" customHeight="1">
       <c r="A560" s="2" t="inlineStr">
@@ -12779,6 +15575,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E560" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="561" ht="20" customHeight="1">
       <c r="A561" s="2" t="inlineStr">
@@ -12801,6 +15602,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E561" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="562" ht="20" customHeight="1">
       <c r="A562" s="2" t="inlineStr">
@@ -12823,6 +15629,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E562" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="563" ht="20" customHeight="1">
       <c r="A563" s="2" t="inlineStr">
@@ -12845,6 +15656,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E563" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="564" ht="20" customHeight="1">
       <c r="A564" s="2" t="inlineStr">
@@ -12867,6 +15683,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E564" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="565" ht="20" customHeight="1">
       <c r="A565" s="2" t="inlineStr">
@@ -12889,6 +15710,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E565" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="566" ht="20" customHeight="1">
       <c r="A566" s="2" t="inlineStr">
@@ -12911,6 +15737,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E566" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="567" ht="20" customHeight="1">
       <c r="A567" s="2" t="inlineStr">
@@ -12933,6 +15764,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E567" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="568" ht="20" customHeight="1">
       <c r="A568" s="2" t="inlineStr">
@@ -12955,6 +15791,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E568" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="569" ht="20" customHeight="1">
       <c r="A569" s="2" t="inlineStr">
@@ -12977,6 +15818,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E569" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="570" ht="20" customHeight="1">
       <c r="A570" s="2" t="inlineStr">
@@ -12999,6 +15845,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E570" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="571" ht="20" customHeight="1">
       <c r="A571" s="2" t="inlineStr">
@@ -13021,6 +15872,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E571" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="572" ht="20" customHeight="1">
       <c r="A572" s="2" t="inlineStr">
@@ -13043,6 +15899,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E572" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="573" ht="20" customHeight="1">
       <c r="A573" s="2" t="inlineStr">
@@ -13065,6 +15926,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E573" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="574" ht="20" customHeight="1">
       <c r="A574" s="2" t="inlineStr">
@@ -13087,6 +15953,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E574" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="575" ht="20" customHeight="1">
       <c r="A575" s="2" t="inlineStr">
@@ -13109,6 +15980,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E575" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="576" ht="20" customHeight="1">
       <c r="A576" s="2" t="inlineStr">
@@ -13131,6 +16007,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E576" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="577" ht="20" customHeight="1">
       <c r="A577" s="2" t="inlineStr">
@@ -13153,6 +16034,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E577" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="578" ht="20" customHeight="1">
       <c r="A578" s="2" t="inlineStr">
@@ -13175,6 +16061,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E578" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="579" ht="20" customHeight="1">
       <c r="A579" s="2" t="inlineStr">
@@ -13197,6 +16088,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E579" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="580" ht="20" customHeight="1">
       <c r="A580" s="2" t="inlineStr">
@@ -13219,6 +16115,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E580" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="581" ht="20" customHeight="1">
       <c r="A581" s="2" t="inlineStr">
@@ -13241,6 +16142,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E581" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="582" ht="20" customHeight="1">
       <c r="A582" s="2" t="inlineStr">
@@ -13263,6 +16169,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E582" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="583" ht="20" customHeight="1">
       <c r="A583" s="2" t="inlineStr">
@@ -13285,6 +16196,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E583" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="584" ht="20" customHeight="1">
       <c r="A584" s="2" t="inlineStr">
@@ -13307,6 +16223,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E584" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="585" ht="20" customHeight="1">
       <c r="A585" s="2" t="inlineStr">
@@ -13329,6 +16250,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E585" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="586" ht="20" customHeight="1">
       <c r="A586" s="2" t="inlineStr">
@@ -13351,6 +16277,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E586" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="587" ht="20" customHeight="1">
       <c r="A587" s="2" t="inlineStr">
@@ -13373,6 +16304,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E587" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="588" ht="20" customHeight="1">
       <c r="A588" s="2" t="inlineStr">
@@ -13395,6 +16331,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E588" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="589" ht="20" customHeight="1">
       <c r="A589" s="2" t="inlineStr">
@@ -13417,6 +16358,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E589" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="590" ht="20" customHeight="1">
       <c r="A590" s="2" t="inlineStr">
@@ -13439,6 +16385,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E590" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="591" ht="20" customHeight="1">
       <c r="A591" s="2" t="inlineStr">
@@ -13461,6 +16412,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E591" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="592" ht="20" customHeight="1">
       <c r="A592" s="2" t="inlineStr">
@@ -13483,6 +16439,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E592" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="593" ht="20" customHeight="1">
       <c r="A593" s="2" t="inlineStr">
@@ -13505,6 +16466,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E593" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="594" ht="20" customHeight="1">
       <c r="A594" s="2" t="inlineStr">
@@ -13527,6 +16493,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E594" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="595" ht="20" customHeight="1">
       <c r="A595" s="2" t="inlineStr">
@@ -13549,6 +16520,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E595" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="596" ht="20" customHeight="1">
       <c r="A596" s="2" t="inlineStr">
@@ -13571,6 +16547,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E596" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="597" ht="20" customHeight="1">
       <c r="A597" s="2" t="inlineStr">
@@ -13593,6 +16574,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E597" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="598" ht="20" customHeight="1">
       <c r="A598" s="2" t="inlineStr">
@@ -13615,6 +16601,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E598" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="599" ht="20" customHeight="1">
       <c r="A599" s="2" t="inlineStr">
@@ -13637,6 +16628,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E599" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="600" ht="20" customHeight="1">
       <c r="A600" s="2" t="inlineStr">
@@ -13659,6 +16655,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E600" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="601" ht="20" customHeight="1">
       <c r="A601" s="2" t="inlineStr">
@@ -13681,6 +16682,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E601" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="602" ht="20" customHeight="1">
       <c r="A602" s="2" t="inlineStr">
@@ -13703,6 +16709,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E602" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="603" ht="20" customHeight="1">
       <c r="A603" s="2" t="inlineStr">
@@ -13725,6 +16736,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E603" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="604" ht="20" customHeight="1">
       <c r="A604" s="2" t="inlineStr">
@@ -13747,6 +16763,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E604" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="605" ht="20" customHeight="1">
       <c r="A605" s="2" t="inlineStr">
@@ -13769,6 +16790,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E605" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="606" ht="20" customHeight="1">
       <c r="A606" s="2" t="inlineStr">
@@ -13791,6 +16817,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E606" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="607" ht="20" customHeight="1">
       <c r="A607" s="2" t="inlineStr">
@@ -13813,6 +16844,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E607" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="608" ht="20" customHeight="1">
       <c r="A608" s="2" t="inlineStr">
@@ -13835,6 +16871,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E608" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="609" ht="20" customHeight="1">
       <c r="A609" s="2" t="inlineStr">
@@ -13857,6 +16898,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E609" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="610" ht="20" customHeight="1">
       <c r="A610" s="2" t="inlineStr">
@@ -13879,6 +16925,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E610" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="611" ht="20" customHeight="1">
       <c r="A611" s="2" t="inlineStr">
@@ -13901,6 +16952,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E611" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="612" ht="20" customHeight="1">
       <c r="A612" s="2" t="inlineStr">
@@ -13923,6 +16979,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E612" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="613" ht="20" customHeight="1">
       <c r="A613" s="2" t="inlineStr">
@@ -13945,6 +17006,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E613" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="614" ht="20" customHeight="1">
       <c r="A614" s="2" t="inlineStr">
@@ -13967,6 +17033,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E614" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="615" ht="20" customHeight="1">
       <c r="A615" s="2" t="inlineStr">
@@ -13989,6 +17060,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E615" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="616" ht="20" customHeight="1">
       <c r="A616" s="2" t="inlineStr">
@@ -14011,6 +17087,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E616" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="617" ht="20" customHeight="1">
       <c r="A617" s="2" t="inlineStr">
@@ -14033,6 +17114,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E617" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="618" ht="20" customHeight="1">
       <c r="A618" s="2" t="inlineStr">
@@ -14055,6 +17141,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E618" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="619" ht="20" customHeight="1">
       <c r="A619" s="2" t="inlineStr">
@@ -14077,6 +17168,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E619" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="620" ht="20" customHeight="1">
       <c r="A620" s="2" t="inlineStr">
@@ -14099,6 +17195,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E620" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="621" ht="20" customHeight="1">
       <c r="A621" s="2" t="inlineStr">
@@ -14121,6 +17222,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E621" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="622" ht="20" customHeight="1">
       <c r="A622" s="2" t="inlineStr">
@@ -14143,6 +17249,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E622" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="623" ht="20" customHeight="1">
       <c r="A623" s="2" t="inlineStr">
@@ -14165,6 +17276,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E623" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="624" ht="20" customHeight="1">
       <c r="A624" s="2" t="inlineStr">
@@ -14187,6 +17303,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E624" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="625" ht="20" customHeight="1">
       <c r="A625" s="2" t="inlineStr">
@@ -14209,6 +17330,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E625" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="626" ht="20" customHeight="1">
       <c r="A626" s="2" t="inlineStr">
@@ -14231,6 +17357,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E626" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="627" ht="20" customHeight="1">
       <c r="A627" s="2" t="inlineStr">
@@ -14253,6 +17384,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E627" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="628" ht="20" customHeight="1">
       <c r="A628" s="2" t="inlineStr">
@@ -14275,6 +17411,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E628" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="629" ht="20" customHeight="1">
       <c r="A629" s="2" t="inlineStr">
@@ -14297,6 +17438,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E629" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="630" ht="20" customHeight="1">
       <c r="A630" s="2" t="inlineStr">
@@ -14319,6 +17465,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E630" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="631" ht="20" customHeight="1">
       <c r="A631" s="2" t="inlineStr">
@@ -14341,6 +17492,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E631" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="632" ht="20" customHeight="1">
       <c r="A632" s="2" t="inlineStr">
@@ -14363,6 +17519,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E632" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="633" ht="20" customHeight="1">
       <c r="A633" s="2" t="inlineStr">
@@ -14385,6 +17546,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E633" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="634" ht="20" customHeight="1">
       <c r="A634" s="2" t="inlineStr">
@@ -14407,6 +17573,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E634" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="635" ht="20" customHeight="1">
       <c r="A635" s="2" t="inlineStr">
@@ -14429,6 +17600,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E635" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="636" ht="20" customHeight="1">
       <c r="A636" s="2" t="inlineStr">
@@ -14451,6 +17627,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E636" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="637" ht="20" customHeight="1">
       <c r="A637" s="2" t="inlineStr">
@@ -14473,6 +17654,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E637" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="638" ht="20" customHeight="1">
       <c r="A638" s="2" t="inlineStr">
@@ -14495,6 +17681,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E638" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="639" ht="20" customHeight="1">
       <c r="A639" s="2" t="inlineStr">
@@ -14517,6 +17708,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E639" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="640" ht="20" customHeight="1">
       <c r="A640" s="2" t="inlineStr">
@@ -14539,6 +17735,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E640" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="641" ht="20" customHeight="1">
       <c r="A641" s="2" t="inlineStr">
@@ -14561,6 +17762,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E641" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="642" ht="20" customHeight="1">
       <c r="A642" s="2" t="inlineStr">
@@ -14583,6 +17789,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E642" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="643" ht="20" customHeight="1">
       <c r="A643" s="2" t="inlineStr">
@@ -14605,6 +17816,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E643" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="644" ht="20" customHeight="1">
       <c r="A644" s="2" t="inlineStr">
@@ -14627,6 +17843,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E644" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="645" ht="20" customHeight="1">
       <c r="A645" s="2" t="inlineStr">
@@ -14649,6 +17870,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E645" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="646" ht="20" customHeight="1">
       <c r="A646" s="2" t="inlineStr">
@@ -14671,6 +17897,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E646" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="647" ht="20" customHeight="1">
       <c r="A647" s="2" t="inlineStr">
@@ -14693,6 +17924,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E647" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="648" ht="20" customHeight="1">
       <c r="A648" s="2" t="inlineStr">
@@ -14715,6 +17951,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E648" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="649" ht="20" customHeight="1">
       <c r="A649" s="2" t="inlineStr">
@@ -14737,6 +17978,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E649" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="650" ht="20" customHeight="1">
       <c r="A650" s="2" t="inlineStr">
@@ -14759,6 +18005,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E650" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="651" ht="20" customHeight="1">
       <c r="A651" s="2" t="inlineStr">
@@ -14781,6 +18032,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E651" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="652" ht="20" customHeight="1">
       <c r="A652" s="2" t="inlineStr">
@@ -14803,6 +18059,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E652" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="653" ht="20" customHeight="1">
       <c r="A653" s="2" t="inlineStr">
@@ -14825,6 +18086,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E653" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="654" ht="20" customHeight="1">
       <c r="A654" s="2" t="inlineStr">
@@ -14847,6 +18113,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E654" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="655" ht="20" customHeight="1">
       <c r="A655" s="2" t="inlineStr">
@@ -14869,6 +18140,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E655" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="656" ht="20" customHeight="1">
       <c r="A656" s="2" t="inlineStr">
@@ -14891,6 +18167,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E656" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="657" ht="20" customHeight="1">
       <c r="A657" s="2" t="inlineStr">
@@ -14913,6 +18194,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E657" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="658" ht="20" customHeight="1">
       <c r="A658" s="2" t="inlineStr">
@@ -14935,6 +18221,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E658" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="659" ht="20" customHeight="1">
       <c r="A659" s="2" t="inlineStr">
@@ -14957,6 +18248,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E659" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="660" ht="20" customHeight="1">
       <c r="A660" s="2" t="inlineStr">
@@ -14979,6 +18275,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E660" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="661" ht="20" customHeight="1">
       <c r="A661" s="2" t="inlineStr">
@@ -15001,6 +18302,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E661" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="662" ht="20" customHeight="1">
       <c r="A662" s="2" t="inlineStr">
@@ -15023,6 +18329,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E662" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="663" ht="20" customHeight="1">
       <c r="A663" s="2" t="inlineStr">
@@ -15045,6 +18356,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E663" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="664" ht="20" customHeight="1">
       <c r="A664" s="2" t="inlineStr">
@@ -15067,6 +18383,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E664" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="665" ht="20" customHeight="1">
       <c r="A665" s="2" t="inlineStr">
@@ -15089,6 +18410,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E665" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="666" ht="20" customHeight="1">
       <c r="A666" s="2" t="inlineStr">
@@ -15111,6 +18437,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E666" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="667" ht="20" customHeight="1">
       <c r="A667" s="2" t="inlineStr">
@@ -15133,6 +18464,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E667" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="668" ht="20" customHeight="1">
       <c r="A668" s="2" t="inlineStr">
@@ -15155,6 +18491,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E668" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="669" ht="20" customHeight="1">
       <c r="A669" s="2" t="inlineStr">
@@ -15177,6 +18518,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E669" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="670" ht="20" customHeight="1">
       <c r="A670" s="2" t="inlineStr">
@@ -15199,6 +18545,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E670" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="671" ht="20" customHeight="1">
       <c r="A671" s="2" t="inlineStr">
@@ -15221,6 +18572,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E671" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="672" ht="20" customHeight="1">
       <c r="A672" s="2" t="inlineStr">
@@ -15243,6 +18599,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E672" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="673" ht="20" customHeight="1">
       <c r="A673" s="2" t="inlineStr">
@@ -15265,6 +18626,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E673" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="674" ht="20" customHeight="1">
       <c r="A674" s="2" t="inlineStr">
@@ -15287,6 +18653,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E674" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="675" ht="20" customHeight="1">
       <c r="A675" s="2" t="inlineStr">
@@ -15309,6 +18680,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E675" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="676" ht="20" customHeight="1">
       <c r="A676" s="2" t="inlineStr">
@@ -15331,6 +18707,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E676" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="677" ht="20" customHeight="1">
       <c r="A677" s="2" t="inlineStr">
@@ -15353,6 +18734,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E677" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="678" ht="20" customHeight="1">
       <c r="A678" s="2" t="inlineStr">
@@ -15375,6 +18761,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E678" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="679" ht="20" customHeight="1">
       <c r="A679" s="2" t="inlineStr">
@@ -15397,6 +18788,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E679" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="680" ht="20" customHeight="1">
       <c r="A680" s="2" t="inlineStr">
@@ -15419,6 +18815,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E680" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="681" ht="20" customHeight="1">
       <c r="A681" s="2" t="inlineStr">
@@ -15441,6 +18842,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E681" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="682" ht="20" customHeight="1">
       <c r="A682" s="2" t="inlineStr">
@@ -15463,6 +18869,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E682" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="683" ht="20" customHeight="1">
       <c r="A683" s="2" t="inlineStr">
@@ -15485,6 +18896,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E683" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="684" ht="20" customHeight="1">
       <c r="A684" s="2" t="inlineStr">
@@ -15507,6 +18923,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E684" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="685" ht="20" customHeight="1">
       <c r="A685" s="2" t="inlineStr">
@@ -15529,6 +18950,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E685" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="686" ht="20" customHeight="1">
       <c r="A686" s="2" t="inlineStr">
@@ -15551,6 +18977,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E686" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="687" ht="20" customHeight="1">
       <c r="A687" s="2" t="inlineStr">
@@ -15573,6 +19004,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E687" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="688" ht="20" customHeight="1">
       <c r="A688" s="2" t="inlineStr">
@@ -15595,6 +19031,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E688" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="689" ht="20" customHeight="1">
       <c r="A689" s="2" t="inlineStr">
@@ -15617,6 +19058,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E689" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="690" ht="20" customHeight="1">
       <c r="A690" s="2" t="inlineStr">
@@ -15639,6 +19085,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E690" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="691" ht="20" customHeight="1">
       <c r="A691" s="2" t="inlineStr">
@@ -15661,6 +19112,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E691" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="692" ht="20" customHeight="1">
       <c r="A692" s="2" t="inlineStr">
@@ -15683,6 +19139,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E692" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="693" ht="20" customHeight="1">
       <c r="A693" s="2" t="inlineStr">
@@ -15705,6 +19166,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E693" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="694" ht="20" customHeight="1">
       <c r="A694" s="2" t="inlineStr">
@@ -15727,6 +19193,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E694" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="695" ht="20" customHeight="1">
       <c r="A695" s="2" t="inlineStr">
@@ -15749,6 +19220,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E695" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="696" ht="20" customHeight="1">
       <c r="A696" s="2" t="inlineStr">
@@ -15771,6 +19247,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E696" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="697" ht="20" customHeight="1">
       <c r="A697" s="2" t="inlineStr">
@@ -15793,6 +19274,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E697" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="698" ht="20" customHeight="1">
       <c r="A698" s="2" t="inlineStr">
@@ -15815,6 +19301,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E698" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="699" ht="20" customHeight="1">
       <c r="A699" s="2" t="inlineStr">
@@ -15837,6 +19328,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E699" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="700" ht="20" customHeight="1">
       <c r="A700" s="2" t="inlineStr">
@@ -15859,6 +19355,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E700" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="701" ht="20" customHeight="1">
       <c r="A701" s="2" t="inlineStr">
@@ -15881,6 +19382,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E701" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="702" ht="20" customHeight="1">
       <c r="A702" s="2" t="inlineStr">
@@ -15903,6 +19409,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E702" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="703" ht="20" customHeight="1">
       <c r="A703" s="2" t="inlineStr">
@@ -15925,6 +19436,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E703" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="704" ht="20" customHeight="1">
       <c r="A704" s="2" t="inlineStr">
@@ -15947,6 +19463,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E704" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="705" ht="20" customHeight="1">
       <c r="A705" s="2" t="inlineStr">
@@ -15969,6 +19490,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E705" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="706" ht="20" customHeight="1">
       <c r="A706" s="2" t="inlineStr">
@@ -15991,6 +19517,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E706" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="707" ht="20" customHeight="1">
       <c r="A707" s="2" t="inlineStr">
@@ -16013,6 +19544,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E707" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="708" ht="20" customHeight="1">
       <c r="A708" s="2" t="inlineStr">
@@ -16035,6 +19571,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E708" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="709" ht="20" customHeight="1">
       <c r="A709" s="2" t="inlineStr">
@@ -16057,6 +19598,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E709" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="710" ht="20" customHeight="1">
       <c r="A710" s="2" t="inlineStr">
@@ -16079,6 +19625,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E710" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="711" ht="20" customHeight="1">
       <c r="A711" s="2" t="inlineStr">
@@ -16101,6 +19652,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E711" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="712" ht="20" customHeight="1">
       <c r="A712" s="2" t="inlineStr">
@@ -16123,6 +19679,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E712" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="713" ht="20" customHeight="1">
       <c r="A713" s="2" t="inlineStr">
@@ -16145,6 +19706,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E713" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="714" ht="20" customHeight="1">
       <c r="A714" s="2" t="inlineStr">
@@ -16167,6 +19733,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E714" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="715" ht="20" customHeight="1">
       <c r="A715" s="2" t="inlineStr">
@@ -16189,6 +19760,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E715" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="716" ht="20" customHeight="1">
       <c r="A716" s="2" t="inlineStr">
@@ -16211,6 +19787,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E716" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="717" ht="20" customHeight="1">
       <c r="A717" s="2" t="inlineStr">
@@ -16233,6 +19814,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E717" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="718" ht="20" customHeight="1">
       <c r="A718" s="2" t="inlineStr">
@@ -16255,6 +19841,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E718" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="719" ht="20" customHeight="1">
       <c r="A719" s="2" t="inlineStr">
@@ -16277,6 +19868,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E719" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="720" ht="20" customHeight="1">
       <c r="A720" s="2" t="inlineStr">
@@ -16299,6 +19895,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E720" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="721" ht="20" customHeight="1">
       <c r="A721" s="2" t="inlineStr">
@@ -16321,6 +19922,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E721" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="722" ht="20" customHeight="1">
       <c r="A722" s="2" t="inlineStr">
@@ -16343,6 +19949,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E722" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="723" ht="20" customHeight="1">
       <c r="A723" s="2" t="inlineStr">
@@ -16365,6 +19976,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E723" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="724" ht="20" customHeight="1">
       <c r="A724" s="2" t="inlineStr">
@@ -16387,6 +20003,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E724" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="725" ht="20" customHeight="1">
       <c r="A725" s="2" t="inlineStr">
@@ -16409,6 +20030,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E725" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="726" ht="20" customHeight="1">
       <c r="A726" s="2" t="inlineStr">
@@ -16431,6 +20057,11 @@
           <t>XII</t>
         </is>
       </c>
+      <c r="E726" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="727" ht="20" customHeight="1">
       <c r="A727" s="2" t="inlineStr">
@@ -16453,6 +20084,11 @@
           <t>GURU</t>
         </is>
       </c>
+      <c r="E727" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="728" ht="20" customHeight="1">
       <c r="A728" s="2" t="inlineStr">
@@ -16475,6 +20111,11 @@
           <t>GURU</t>
         </is>
       </c>
+      <c r="E728" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="729" ht="20" customHeight="1">
       <c r="A729" s="2" t="inlineStr">
@@ -16497,6 +20138,11 @@
           <t>GURU</t>
         </is>
       </c>
+      <c r="E729" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="730" ht="20" customHeight="1">
       <c r="A730" s="2" t="inlineStr">
@@ -16519,6 +20165,11 @@
           <t>GURU</t>
         </is>
       </c>
+      <c r="E730" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="731" ht="20" customHeight="1">
       <c r="A731" s="2" t="inlineStr">
@@ -16541,6 +20192,11 @@
           <t>GURU</t>
         </is>
       </c>
+      <c r="E731" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="732" ht="20" customHeight="1">
       <c r="A732" s="2" t="inlineStr">
@@ -16563,6 +20219,11 @@
           <t>GURU</t>
         </is>
       </c>
+      <c r="E732" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="733" ht="20" customHeight="1">
       <c r="A733" s="2" t="inlineStr">
@@ -16585,6 +20246,11 @@
           <t>GURU</t>
         </is>
       </c>
+      <c r="E733" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="734" ht="20" customHeight="1">
       <c r="A734" s="2" t="inlineStr">
@@ -16607,6 +20273,11 @@
           <t>GURU</t>
         </is>
       </c>
+      <c r="E734" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="735" ht="20" customHeight="1">
       <c r="A735" s="2" t="inlineStr">
@@ -16629,6 +20300,11 @@
           <t>GURU</t>
         </is>
       </c>
+      <c r="E735" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="736" ht="20" customHeight="1">
       <c r="A736" s="2" t="inlineStr">
@@ -16651,6 +20327,11 @@
           <t>GURU</t>
         </is>
       </c>
+      <c r="E736" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="737" ht="20" customHeight="1">
       <c r="A737" s="2" t="inlineStr">
@@ -16673,6 +20354,11 @@
           <t>GURU</t>
         </is>
       </c>
+      <c r="E737" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="738" ht="20" customHeight="1">
       <c r="A738" s="2" t="inlineStr">
@@ -16695,6 +20381,11 @@
           <t>GURU</t>
         </is>
       </c>
+      <c r="E738" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="739" ht="20" customHeight="1">
       <c r="A739" s="2" t="inlineStr">
@@ -16717,6 +20408,11 @@
           <t>GURU</t>
         </is>
       </c>
+      <c r="E739" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="740" ht="20" customHeight="1">
       <c r="A740" s="2" t="inlineStr">
@@ -16739,6 +20435,11 @@
           <t>GURU</t>
         </is>
       </c>
+      <c r="E740" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="741" ht="20" customHeight="1">
       <c r="A741" s="2" t="inlineStr">
@@ -16761,6 +20462,11 @@
           <t>GURU</t>
         </is>
       </c>
+      <c r="E741" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="742" ht="20" customHeight="1">
       <c r="A742" s="2" t="inlineStr">
@@ -16783,6 +20489,11 @@
           <t>GURU</t>
         </is>
       </c>
+      <c r="E742" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="743" ht="20" customHeight="1">
       <c r="A743" s="2" t="inlineStr">
@@ -16805,6 +20516,11 @@
           <t>GURU</t>
         </is>
       </c>
+      <c r="E743" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="744" ht="20" customHeight="1">
       <c r="A744" s="2" t="inlineStr">
@@ -16827,6 +20543,11 @@
           <t>GURU</t>
         </is>
       </c>
+      <c r="E744" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="745" ht="20" customHeight="1">
       <c r="A745" s="2" t="inlineStr">
@@ -16849,6 +20570,11 @@
           <t>GURU</t>
         </is>
       </c>
+      <c r="E745" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="746" ht="20" customHeight="1">
       <c r="A746" s="2" t="inlineStr">
@@ -16871,6 +20597,11 @@
           <t>GURU</t>
         </is>
       </c>
+      <c r="E746" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="747" ht="20" customHeight="1">
       <c r="A747" s="2" t="inlineStr">
@@ -16893,6 +20624,11 @@
           <t>GURU</t>
         </is>
       </c>
+      <c r="E747" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="748" ht="20" customHeight="1">
       <c r="A748" s="2" t="inlineStr">
@@ -16915,6 +20651,11 @@
           <t>GURU</t>
         </is>
       </c>
+      <c r="E748" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="749" ht="20" customHeight="1">
       <c r="A749" s="2" t="inlineStr">
@@ -16937,6 +20678,11 @@
           <t>GURU</t>
         </is>
       </c>
+      <c r="E749" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="750" ht="20" customHeight="1">
       <c r="A750" s="2" t="inlineStr">
@@ -16959,6 +20705,11 @@
           <t>GURU</t>
         </is>
       </c>
+      <c r="E750" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="751" ht="20" customHeight="1">
       <c r="A751" s="2" t="inlineStr">
@@ -16981,6 +20732,11 @@
           <t>GURU</t>
         </is>
       </c>
+      <c r="E751" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="752" ht="20" customHeight="1">
       <c r="A752" s="2" t="inlineStr">
@@ -17003,6 +20759,11 @@
           <t>GURU</t>
         </is>
       </c>
+      <c r="E752" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="753" ht="20" customHeight="1">
       <c r="A753" s="2" t="inlineStr">
@@ -17025,6 +20786,11 @@
           <t>GURU</t>
         </is>
       </c>
+      <c r="E753" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="754" ht="20" customHeight="1">
       <c r="A754" s="2" t="inlineStr">
@@ -17047,6 +20813,11 @@
           <t>GURU</t>
         </is>
       </c>
+      <c r="E754" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="755" ht="20" customHeight="1">
       <c r="A755" s="2" t="inlineStr">
@@ -17069,6 +20840,11 @@
           <t>GURU</t>
         </is>
       </c>
+      <c r="E755" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="756" ht="20" customHeight="1">
       <c r="A756" s="2" t="inlineStr">
@@ -17091,6 +20867,11 @@
           <t>GURU</t>
         </is>
       </c>
+      <c r="E756" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="757" ht="20" customHeight="1">
       <c r="A757" s="2" t="inlineStr">
@@ -17113,6 +20894,11 @@
           <t>GURU</t>
         </is>
       </c>
+      <c r="E757" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="758" ht="20" customHeight="1">
       <c r="A758" s="2" t="inlineStr">
@@ -17135,6 +20921,11 @@
           <t>GURU</t>
         </is>
       </c>
+      <c r="E758" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="759" ht="20" customHeight="1">
       <c r="A759" s="2" t="inlineStr">
@@ -17157,6 +20948,11 @@
           <t>GURU</t>
         </is>
       </c>
+      <c r="E759" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="760" ht="20" customHeight="1">
       <c r="A760" s="2" t="inlineStr">
@@ -17179,6 +20975,11 @@
           <t>GURU</t>
         </is>
       </c>
+      <c r="E760" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="761" ht="20" customHeight="1">
       <c r="A761" s="2" t="inlineStr">
@@ -17201,6 +21002,11 @@
           <t>GURU</t>
         </is>
       </c>
+      <c r="E761" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="762" ht="20" customHeight="1">
       <c r="A762" s="2" t="inlineStr">
@@ -17223,6 +21029,11 @@
           <t>GURU</t>
         </is>
       </c>
+      <c r="E762" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="763" ht="20" customHeight="1">
       <c r="A763" s="2" t="inlineStr">
@@ -17245,6 +21056,11 @@
           <t>GURU</t>
         </is>
       </c>
+      <c r="E763" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="764" ht="20" customHeight="1">
       <c r="A764" s="2" t="inlineStr">
@@ -17267,6 +21083,11 @@
           <t>GURU</t>
         </is>
       </c>
+      <c r="E764" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="765" ht="20" customHeight="1">
       <c r="A765" s="2" t="inlineStr">
@@ -17289,6 +21110,11 @@
           <t>GURU</t>
         </is>
       </c>
+      <c r="E765" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="766" ht="20" customHeight="1">
       <c r="A766" s="2" t="inlineStr">
@@ -17311,6 +21137,11 @@
           <t>GURU</t>
         </is>
       </c>
+      <c r="E766" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="767" ht="20" customHeight="1">
       <c r="A767" s="2" t="inlineStr">
@@ -17333,6 +21164,11 @@
           <t>GURU</t>
         </is>
       </c>
+      <c r="E767" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
     </row>
     <row r="768" ht="20" customHeight="1">
       <c r="A768" s="2" t="inlineStr">
@@ -17355,6 +21191,11 @@
           <t>GURU</t>
         </is>
       </c>
+      <c r="E768" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="769" ht="20" customHeight="1">
       <c r="A769" s="2" t="inlineStr">
@@ -17377,6 +21218,11 @@
           <t>TENDIK</t>
         </is>
       </c>
+      <c r="E769" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="770" ht="20" customHeight="1">
       <c r="A770" s="2" t="inlineStr">
@@ -17399,6 +21245,11 @@
           <t>TENDIK</t>
         </is>
       </c>
+      <c r="E770" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="771" ht="20" customHeight="1">
       <c r="A771" s="2" t="inlineStr">
@@ -17421,6 +21272,11 @@
           <t>TENDIK</t>
         </is>
       </c>
+      <c r="E771" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="772" ht="20" customHeight="1">
       <c r="A772" s="2" t="inlineStr">
@@ -17443,6 +21299,11 @@
           <t>TENDIK</t>
         </is>
       </c>
+      <c r="E772" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="773" ht="20" customHeight="1">
       <c r="A773" s="2" t="inlineStr">
@@ -17465,6 +21326,11 @@
           <t>TENDIK</t>
         </is>
       </c>
+      <c r="E773" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="774" ht="20" customHeight="1">
       <c r="A774" s="2" t="inlineStr">
@@ -17485,6 +21351,11 @@
       <c r="D774" s="4" t="inlineStr">
         <is>
           <t>TENDIK</t>
+        </is>
+      </c>
+      <c r="E774" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
     </row>
